--- a/حركات الشركات للأسنان - جديد/WAAD_Transactions.xlsx
+++ b/حركات الشركات للأسنان - جديد/WAAD_Transactions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\حركات الشركات للأسنان - جديد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79E5B8D-E9BB-42CC-BDEA-CBB272BC284E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A17F192-91A4-4ED8-9769-46BDA8DAB630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,12 +272,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -292,8 +298,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,7 +641,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.81640625" customWidth="1"/>
     <col min="2" max="2" width="22.81640625" customWidth="1"/>
@@ -644,7 +651,7 @@
     <col min="7" max="7" width="35.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +674,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -690,7 +697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -713,7 +720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -736,7 +743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -759,7 +766,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -782,7 +789,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -805,7 +812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -828,7 +835,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -851,7 +858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -874,7 +881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -897,7 +904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -920,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -943,7 +950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -966,7 +973,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -989,7 +996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1012,7 +1019,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1035,7 +1042,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -1058,7 +1065,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -1081,7 +1088,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -1104,7 +1111,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -1127,7 +1134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -1150,49 +1157,49 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>450</v>
       </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>325</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="F24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>21</v>
       </c>
     </row>
